--- a/data/inquiries.xlsx
+++ b/data/inquiries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\VERZOLLA\EXCEL\Fabio Rivolta\DEVOIRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECCC05C-27C4-4E7E-ABCB-863584246EAC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58487348-B6EE-4A5B-955E-31FC4422EFEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{E699D23F-0A2E-42F4-A57F-BA26595CA428}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Buongiorno,
 avrei bisogno vs miglior offerta per
@@ -150,6 +150,111 @@
 NATV25-PP-A  INA/ELGES CUSCINETTO    N. 8 ST
 Cordiali Saluti</t>
   </si>
+  <si>
+    <t>InquiryBody</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ConversationID</t>
+  </si>
+  <si>
+    <t>InquiryFrom</t>
+  </si>
+  <si>
+    <t>InquirySubject</t>
+  </si>
+  <si>
+    <t>InquiryDate</t>
+  </si>
+  <si>
+    <t>Processed</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>RICHIESTA OFFERTA</t>
+  </si>
+  <si>
+    <t>RICHIESTA QUOTAZIONE</t>
+  </si>
+  <si>
+    <t>INQUIRY</t>
+  </si>
+  <si>
+    <t>OFFERTA</t>
+  </si>
+  <si>
+    <t>INQUIRY REQUEST</t>
+  </si>
+  <si>
+    <t>RICHIESTA DI OFFERTA</t>
+  </si>
+  <si>
+    <t>OFFERTA FORNITORE</t>
+  </si>
+  <si>
+    <t>RIVENDITORE_1</t>
+  </si>
+  <si>
+    <t>RIVENDITORE_2</t>
+  </si>
+  <si>
+    <t>CLIENTE_1</t>
+  </si>
+  <si>
+    <t>MANUTENTORE_1</t>
+  </si>
+  <si>
+    <t>CLIENTE_2</t>
+  </si>
+  <si>
+    <t>MANUTENTORE_2</t>
+  </si>
+  <si>
+    <t>RIVENDITORE_3</t>
+  </si>
+  <si>
+    <t>CLIENTE_3</t>
+  </si>
+  <si>
+    <t>CLIENTE_5</t>
+  </si>
+  <si>
+    <t>RIVENDITORE_8</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
 </sst>
 </file>
 
@@ -184,10 +289,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -210,15 +321,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>50788</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>2106516</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>885825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -558,60 +669,247 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C93F6D7-0C8D-46B7-99FF-2C831A22D6D9}">
-  <dimension ref="B1:B10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="34.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="34.5703125" style="1"/>
+    <col min="5" max="5" width="34.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="34.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="285" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="285" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="2:2" ht="150" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="F2" s="3">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="F3" s="3">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <f t="shared" ref="A4:A11" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="2:2" ht="165" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="3">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="2:2" ht="225" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="3">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="225" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="2:2" ht="255" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="3">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="255" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="2:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
+      <c r="F7" s="3">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="2:2" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
+      <c r="F8" s="3">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="2:2" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
+      <c r="F9" s="3">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="2:2" ht="165" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
+      <c r="F10" s="3">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>9</v>
+      </c>
+      <c r="F11" s="3">
+        <v>46181</v>
       </c>
     </row>
   </sheetData>

--- a/data/inquiries.xlsx
+++ b/data/inquiries.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\VERZOLLA\EXCEL\Fabio Rivolta\DEVOIRS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\VERZOLLA\EXCEL\Fabio Rivolta\DEVOIRS\CODE_MATCHING\CATALISTINI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58487348-B6EE-4A5B-955E-31FC4422EFEF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF511971-2C04-4A8B-BA56-D20C34024B7F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{E699D23F-0A2E-42F4-A57F-BA26595CA428}"/>
   </bookViews>
@@ -25,7 +25,76 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>InquiryBody</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ConversationID</t>
+  </si>
+  <si>
+    <t>InquiryFrom</t>
+  </si>
+  <si>
+    <t>InquirySubject</t>
+  </si>
+  <si>
+    <t>InquiryDate</t>
+  </si>
+  <si>
+    <t>Processed</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>RICHIESTA OFFERTA</t>
+  </si>
+  <si>
+    <t>RICHIESTA QUOTAZIONE</t>
+  </si>
+  <si>
+    <t>INQUIRY</t>
+  </si>
+  <si>
+    <t>OFFERTA</t>
+  </si>
+  <si>
+    <t>INQUIRY REQUEST</t>
+  </si>
+  <si>
+    <t>RIVENDITORE_1</t>
+  </si>
+  <si>
+    <t>RIVENDITORE_2</t>
+  </si>
+  <si>
+    <t>CLIENTE_1</t>
+  </si>
+  <si>
+    <t>MANUTENTORE_1</t>
+  </si>
+  <si>
+    <t>CLIENTE_2</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
   <si>
     <t>Buongiorno,
 avrei bisogno vs miglior offerta per
@@ -33,19 +102,22 @@
 CUSCINETTO A SFERE 6011 (55*90*18)
 1
 CUSCINETTO 6012 (60*95*18)
-In attesa</t>
+In attesa,
+Mario Rossi
+Account Manager
+Cuscinetti BimBumBam</t>
+  </si>
+  <si>
+    <t>La presente per chiedere offerta per:</t>
   </si>
   <si>
     <t>Buongiorno,
 La presente per chiedere offerta per:
-Pz 200 BOCCOLA BRONZO SINT.CILIND:BR 22X28X30
+PUNTA PER LEGNO FORSTNER 28 mm
 Resto in attesa di un Vostro gentile riscontro
-Grazie</t>
-  </si>
-  <si>
-    <t>Buongiorno
-Mi dareste il costo aggiornato.
-N° 4pz. CUSC. ORIENTABILE A RULLI 22214</t>
+Grazie.
+Marino Kesslner
+Wunderbare Kuegellager</t>
   </si>
   <si>
     <t>Buongiorno, ci necessita cortesemente entro questa mattina vs. migliore offerta e verifica tempi di consegna/disponibilità per:
@@ -53,207 +125,21 @@
 n.2   Coppie tenute SKF TSN 507 L (TXL507)
 n.2   Cuscinetto SKF 2207K
 n.2   Bussola SKF H307
-n.2   Anelli arresto SKF FRB 5.5/72</t>
-  </si>
-  <si>
-    <t>Inquiry no QTY26-016-2289PO
-No.
-Designation
-Brand
-Description
-Quantity
+n.2   Anelli arresto SKF FRB 5.5/72
+Cordialità,
+Ettore Fierramosca
+Soldatini Ricambi SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inquiry no QTY26-016-2289PO
+No. 1
+Designation: 365/363D
+Brand: TIMKEN 
+Description: Double row tapered roller bearing
+Quantity: 2 pcs
 Unit
 Comment
-1.
-365/363D
-TIMKEN
-Double row tapered roller bearing
-2
-pcs</t>
-  </si>
-  <si>
-    <t>Buongiorno,
-mi servirebbe sapere costi e disponibilità per il seguente materiale , nel dettaglio :
-I.ME.TO.MAGR.0002.05 Mole a Disco Grigie - 7000G 150 20M- SCU            N.2
-                                                   Alternativa a nostra Mola Widia D150X20X16 9/80K
-I.ME.TR.BEFL.0001.05 Supporto a Flangia 3 Fori UCFB 204 D.20 (Ghisa)    N.6
-In attesa vostro riscontro
-Cordiali Saluti</t>
-  </si>
-  <si>
-    <t>Buonasera, avrei bisogno di acquistare 4 elettrovalvole come quella nell'immagine allegata.
-Riuscite a quotarcele?
-Ringrazio anticipatamente e saluto</t>
-  </si>
-  <si>
-    <t>Buongiorno,
-per cortesia, fornire vostro migliore offerta per quanto riportato di seguito:
-OR
-Secondo Cod. art.
-Descrizione Riga
-Descrizione Riga 2
-Nome del produttore
-Numero di articolo del produttore
-Q.tà
-11465106
-15081645
-W75UD30 10 P100 B5/B3
-RIDUTTORE I=10 VER ALB.LENTO C
-Bonfiglioli
-W75UD30 10 P100 B5/B3
-1
-Si raccomanda di procedere alla consegna solo dopo averci inviato la vostra offerta formale ed aver ricevuto il relativo ordine OP, da riportare in bolla.
-Resto a disposizione per qualsiasi chiarimento o delucidazione in merito alle specifiche tecniche dei materiali richiesti.
-Vi prego di rispondere facendo riferimento alla presente e-mail per facilitare la gestione degli ordini.
-Grazie per la collaborazione.
-Cordiali Saluti - Best Regards</t>
-  </si>
-  <si>
-    <t>Buongiorno,
-con la presente siamo a chiedere Vostre migliori condizioni per l’eventuale fornitura di:
-Codice Ricambio
-Descrizione
-Quantita'
-Manufacturer
-Manufacturer Part Number
-SP1050250
-BUSSOLA DI TRAZIONE H 313
-1.0
-SKF
-SP1050252
-GUARNIZIONE TSN 513C
-2.0
-SKF
-SP1050232
-CUSCINETTO CON SUPPORTO FORMA OMEGA SY 45 TF
-10.0
-SKF
-SY 45 TF
-SP1050221
-CUSCINETTO CON SUPPORTO FORMA QUADRATA FY 50 TF
-4.0
-SKF
-FY 50 TF
-SP1050251
-CUSCINETTO 32215J
-4.0
-SKF
-SP1050253
-SUPPORTO SNL 513-611
-2.0
-SKF
-Cordiali Saluti</t>
-  </si>
-  <si>
-    <t>Buongiorno,
-mi servirebbe offerta e tempi di consegna per cuscinetto sotto indicato
-NATV25-PP-A  INA/ELGES CUSCINETTO    N. 8 ST
-Cordiali Saluti</t>
-  </si>
-  <si>
-    <t>InquiryBody</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>ConversationID</t>
-  </si>
-  <si>
-    <t>InquiryFrom</t>
-  </si>
-  <si>
-    <t>InquirySubject</t>
-  </si>
-  <si>
-    <t>InquiryDate</t>
-  </si>
-  <si>
-    <t>Processed</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>RICHIESTA OFFERTA</t>
-  </si>
-  <si>
-    <t>RICHIESTA QUOTAZIONE</t>
-  </si>
-  <si>
-    <t>INQUIRY</t>
-  </si>
-  <si>
-    <t>OFFERTA</t>
-  </si>
-  <si>
-    <t>INQUIRY REQUEST</t>
-  </si>
-  <si>
-    <t>RICHIESTA DI OFFERTA</t>
-  </si>
-  <si>
-    <t>OFFERTA FORNITORE</t>
-  </si>
-  <si>
-    <t>RIVENDITORE_1</t>
-  </si>
-  <si>
-    <t>RIVENDITORE_2</t>
-  </si>
-  <si>
-    <t>CLIENTE_1</t>
-  </si>
-  <si>
-    <t>MANUTENTORE_1</t>
-  </si>
-  <si>
-    <t>CLIENTE_2</t>
-  </si>
-  <si>
-    <t>MANUTENTORE_2</t>
-  </si>
-  <si>
-    <t>RIVENDITORE_3</t>
-  </si>
-  <si>
-    <t>CLIENTE_3</t>
-  </si>
-  <si>
-    <t>CLIENTE_5</t>
-  </si>
-  <si>
-    <t>RIVENDITORE_8</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>L</t>
+</t>
   </si>
 </sst>
 </file>
@@ -315,61 +201,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>50788</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2106516</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>885825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Immagine 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7A35D7F-EF34-48F1-A1D0-83FD2DCA17D7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="4848225" y="14909788"/>
-          <a:ext cx="1858866" cy="835037"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -669,253 +500,153 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C93F6D7-0C8D-46B7-99FF-2C831A22D6D9}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="34.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="34.5703125" style="1"/>
+    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="34.5703125" style="1"/>
+    <col min="6" max="6" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="34.5703125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="285" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="345" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3">
         <v>46208</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3">
         <v>46208</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A11" si="0">A3+1</f>
+        <f t="shared" ref="A4:A6" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F4" s="3">
         <v>46206</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="240" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
         <v>46208</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="225" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
         <v>46230</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="255" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="3">
-        <v>46215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="3">
-        <v>46208</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="3">
-        <v>46208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="3">
-        <v>46181</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
